--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/2.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/2.xlsx
@@ -426,13 +426,13 @@
         <v>-16.99305279366321</v>
       </c>
       <c r="E2">
-        <v>-16.70791108290956</v>
+        <v>-14.80115181723988</v>
       </c>
       <c r="F2">
-        <v>-1.837078820109999</v>
+        <v>-1.527202313703357</v>
       </c>
       <c r="G2">
-        <v>-12.09536067476645</v>
+        <v>-9.482608613717309</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-17.0394828876946</v>
       </c>
       <c r="E3">
-        <v>-17.20593454037712</v>
+        <v>-13.93946019763834</v>
       </c>
       <c r="F3">
-        <v>-1.86870754428369</v>
+        <v>-1.235285640956812</v>
       </c>
       <c r="G3">
-        <v>-11.47985411646854</v>
+        <v>-8.596411988855344</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-16.911478632975</v>
       </c>
       <c r="E4">
-        <v>-17.24482054668098</v>
+        <v>-13.94863941445189</v>
       </c>
       <c r="F4">
-        <v>-1.477840728537938</v>
+        <v>-1.06767378067436</v>
       </c>
       <c r="G4">
-        <v>-11.71945153932775</v>
+        <v>-8.766666724848982</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-16.58341848603329</v>
       </c>
       <c r="E5">
-        <v>-17.51416965218321</v>
+        <v>-15.89656250885129</v>
       </c>
       <c r="F5">
-        <v>-1.68982243201654</v>
+        <v>-1.320566893442424</v>
       </c>
       <c r="G5">
-        <v>-11.35458969435359</v>
+        <v>-9.032294967283484</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-16.08038103737638</v>
       </c>
       <c r="E6">
-        <v>-18.70496812029219</v>
+        <v>-15.60073994430023</v>
       </c>
       <c r="F6">
-        <v>-1.98015443792153</v>
+        <v>-1.235948334879051</v>
       </c>
       <c r="G6">
-        <v>-11.55741357736258</v>
+        <v>-8.691126696733892</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-15.40207445018114</v>
       </c>
       <c r="E7">
-        <v>-18.54437031808417</v>
+        <v>-16.37235115894119</v>
       </c>
       <c r="F7">
-        <v>-1.456059636048727</v>
+        <v>-1.002377720148689</v>
       </c>
       <c r="G7">
-        <v>-11.23148374793026</v>
+        <v>-9.474501087691634</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.58582592794857</v>
       </c>
       <c r="E8">
-        <v>-19.69417703947572</v>
+        <v>-17.15049243310121</v>
       </c>
       <c r="F8">
-        <v>-1.229989059783312</v>
+        <v>-0.953718590540843</v>
       </c>
       <c r="G8">
-        <v>-10.61532832270664</v>
+        <v>-9.43926364097163</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.65927349345487</v>
       </c>
       <c r="E9">
-        <v>-20.77997830924285</v>
+        <v>-18.36276492495456</v>
       </c>
       <c r="F9">
-        <v>-1.622272383787851</v>
+        <v>-0.3669660783202859</v>
       </c>
       <c r="G9">
-        <v>-10.68420753319672</v>
+        <v>-9.124314891093066</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-12.63640071247417</v>
       </c>
       <c r="E10">
-        <v>-21.34743685867002</v>
+        <v>-18.89417682128067</v>
       </c>
       <c r="F10">
-        <v>-1.524837324768365</v>
+        <v>-0.8577721077441874</v>
       </c>
       <c r="G10">
-        <v>-11.24195831401651</v>
+        <v>-8.496201775381605</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-11.55376651757257</v>
       </c>
       <c r="E11">
-        <v>-22.55561108154643</v>
+        <v>-19.56645143008938</v>
       </c>
       <c r="F11">
-        <v>-1.181663762238794</v>
+        <v>-0.9985722003002278</v>
       </c>
       <c r="G11">
-        <v>-10.81476551762896</v>
+        <v>-7.4954470326787</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.43014618471273</v>
       </c>
       <c r="E12">
-        <v>-22.67772591163727</v>
+        <v>-20.08592626893126</v>
       </c>
       <c r="F12">
-        <v>-1.028825834585271</v>
+        <v>-0.8811966811605518</v>
       </c>
       <c r="G12">
-        <v>-9.846119756111442</v>
+        <v>-7.172056391674994</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.269882654040169</v>
       </c>
       <c r="E13">
-        <v>-23.27596902736858</v>
+        <v>-21.76572747428452</v>
       </c>
       <c r="F13">
-        <v>-1.001587457646418</v>
+        <v>-0.5091205515799035</v>
       </c>
       <c r="G13">
-        <v>-9.636592018385429</v>
+        <v>-6.595905598747933</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.10077376155866</v>
       </c>
       <c r="E14">
-        <v>-23.78415890898335</v>
+        <v>-21.93065449764388</v>
       </c>
       <c r="F14">
-        <v>-1.174885231781686</v>
+        <v>-0.09897679800360389</v>
       </c>
       <c r="G14">
-        <v>-8.898899845324092</v>
+        <v>-6.187460421749272</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-6.928200848079983</v>
       </c>
       <c r="E15">
-        <v>-25.06876471616123</v>
+        <v>-23.44982167299705</v>
       </c>
       <c r="F15">
-        <v>-0.8500981121246528</v>
+        <v>-0.4466467387955704</v>
       </c>
       <c r="G15">
-        <v>-8.460901428296356</v>
+        <v>-5.645540669698274</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.759173006846882</v>
       </c>
       <c r="E16">
-        <v>-25.16536159521884</v>
+        <v>-24.69230814342959</v>
       </c>
       <c r="F16">
-        <v>-0.5834988323098683</v>
+        <v>0.179697593441789</v>
       </c>
       <c r="G16">
-        <v>-7.882704718226026</v>
+        <v>-4.903130969243476</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.614584360740914</v>
       </c>
       <c r="E17">
-        <v>-26.92516735086561</v>
+        <v>-25.13646993104991</v>
       </c>
       <c r="F17">
-        <v>-0.8551677206297857</v>
+        <v>-0.06419779259706664</v>
       </c>
       <c r="G17">
-        <v>-6.67150190613719</v>
+        <v>-3.414666657695139</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-3.501624771256739</v>
       </c>
       <c r="E18">
-        <v>-26.23537660459524</v>
+        <v>-26.35736010893986</v>
       </c>
       <c r="F18">
-        <v>-0.477482715364782</v>
+        <v>0.2696276437919117</v>
       </c>
       <c r="G18">
-        <v>-6.71797203387194</v>
+        <v>-4.523894735537803</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-2.436424945371617</v>
       </c>
       <c r="E19">
-        <v>-28.03109768759685</v>
+        <v>-26.55123313815624</v>
       </c>
       <c r="F19">
-        <v>0.06964981234727748</v>
+        <v>0.5145725713301144</v>
       </c>
       <c r="G19">
-        <v>-5.533256896642814</v>
+        <v>-3.623717676863497</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.438243057474547</v>
       </c>
       <c r="E20">
-        <v>-29.55866744647125</v>
+        <v>-27.67687139376886</v>
       </c>
       <c r="F20">
-        <v>-0.1459021546373903</v>
+        <v>0.4319280122876132</v>
       </c>
       <c r="G20">
-        <v>-4.518104591389618</v>
+        <v>-2.599951332117118</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.5165986801859304</v>
       </c>
       <c r="E21">
-        <v>-29.16705633547294</v>
+        <v>-28.02336305399174</v>
       </c>
       <c r="F21">
-        <v>0.2772312281822084</v>
+        <v>1.007987958072834</v>
       </c>
       <c r="G21">
-        <v>-5.712496453230035</v>
+        <v>-1.910695750840857</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.3123922711938293</v>
       </c>
       <c r="E22">
-        <v>-30.04814340924933</v>
+        <v>-28.42171479855048</v>
       </c>
       <c r="F22">
-        <v>0.03138917874677392</v>
+        <v>1.141820652403928</v>
       </c>
       <c r="G22">
-        <v>-6.085320160226138</v>
+        <v>-2.104405701980232</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.037504680469994</v>
       </c>
       <c r="E23">
-        <v>-30.58771561573726</v>
+        <v>-29.7221747932292</v>
       </c>
       <c r="F23">
-        <v>0.431982684536198</v>
+        <v>0.7874864958564395</v>
       </c>
       <c r="G23">
-        <v>-4.596643973763288</v>
+        <v>-1.754229437018282</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.655878481181926</v>
       </c>
       <c r="E24">
-        <v>-31.39279904600592</v>
+        <v>-28.1294878423615</v>
       </c>
       <c r="F24">
-        <v>0.4083013172249658</v>
+        <v>1.132037633376866</v>
       </c>
       <c r="G24">
-        <v>-3.702223953781774</v>
+        <v>-0.8198279585589899</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.158418574736484</v>
       </c>
       <c r="E25">
-        <v>-31.6557471534983</v>
+        <v>-29.12817485764308</v>
       </c>
       <c r="F25">
-        <v>0.7008177279711384</v>
+        <v>1.134956800104331</v>
       </c>
       <c r="G25">
-        <v>-3.684783999880893</v>
+        <v>-1.617755507707367</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.543203612456655</v>
       </c>
       <c r="E26">
-        <v>-31.20661762989156</v>
+        <v>-29.39071766671178</v>
       </c>
       <c r="F26">
-        <v>0.6678346230938704</v>
+        <v>0.8424470162973811</v>
       </c>
       <c r="G26">
-        <v>-4.396571154097434</v>
+        <v>-1.515588761819919</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.814089341411636</v>
       </c>
       <c r="E27">
-        <v>-31.7473174264074</v>
+        <v>-30.60016212654734</v>
       </c>
       <c r="F27">
-        <v>0.9277721722553414</v>
+        <v>1.539823024957395</v>
       </c>
       <c r="G27">
-        <v>-4.24319026871746</v>
+        <v>-1.918912524869328</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.971136699066155</v>
       </c>
       <c r="E28">
-        <v>-31.06043396044996</v>
+        <v>-30.36513432554925</v>
       </c>
       <c r="F28">
-        <v>0.3129355199776727</v>
+        <v>0.9396923791816262</v>
       </c>
       <c r="G28">
-        <v>-3.892888203025019</v>
+        <v>-1.917488990287441</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.022989445595613</v>
       </c>
       <c r="E29">
-        <v>-31.45360965921792</v>
+        <v>-30.0158327472046</v>
       </c>
       <c r="F29">
-        <v>0.8816006299581025</v>
+        <v>1.310668436851357</v>
       </c>
       <c r="G29">
-        <v>-4.567425098833681</v>
+        <v>-1.466612551111941</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.979954610257598</v>
       </c>
       <c r="E30">
-        <v>-31.30657010818886</v>
+        <v>-29.54196643433097</v>
       </c>
       <c r="F30">
-        <v>0.7752796738087859</v>
+        <v>1.209476731660175</v>
       </c>
       <c r="G30">
-        <v>-3.762542093507295</v>
+        <v>-1.461785775715684</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.850400687034632</v>
       </c>
       <c r="E31">
-        <v>-31.22604931185847</v>
+        <v>-29.52296269315778</v>
       </c>
       <c r="F31">
-        <v>0.5416220805011294</v>
+        <v>1.191574055350872</v>
       </c>
       <c r="G31">
-        <v>-4.404761443761591</v>
+        <v>-2.06652975046543</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.644553053578496</v>
       </c>
       <c r="E32">
-        <v>-31.384582129919</v>
+        <v>-28.61571462503908</v>
       </c>
       <c r="F32">
-        <v>0.6033122577224141</v>
+        <v>0.686036340035584</v>
       </c>
       <c r="G32">
-        <v>-4.743469978975504</v>
+        <v>-1.993009155129295</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.369288759902971</v>
       </c>
       <c r="E33">
-        <v>-30.28512071830772</v>
+        <v>-27.25742601728239</v>
       </c>
       <c r="F33">
-        <v>0.0496729040613646</v>
+        <v>0.5827223575584297</v>
       </c>
       <c r="G33">
-        <v>-4.39677309737533</v>
+        <v>-1.023436440860786</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>2.029865983708159</v>
       </c>
       <c r="E34">
-        <v>-30.05625617043407</v>
+        <v>-28.65423382494832</v>
       </c>
       <c r="F34">
-        <v>0.1308032074915482</v>
+        <v>0.6418578497094808</v>
       </c>
       <c r="G34">
-        <v>-4.75634469057773</v>
+        <v>-2.464798310476371</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.633835289495215</v>
       </c>
       <c r="E35">
-        <v>-29.26921870908598</v>
+        <v>-28.45149404362492</v>
       </c>
       <c r="F35">
-        <v>0.4067522701817307</v>
+        <v>1.153807128722437</v>
       </c>
       <c r="G35">
-        <v>-4.223535559850808</v>
+        <v>-2.662977498093762</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.186191450347467</v>
       </c>
       <c r="E36">
-        <v>-29.91879660616824</v>
+        <v>-27.20631765963183</v>
       </c>
       <c r="F36">
-        <v>0.3083919247733174</v>
+        <v>1.275255730381678</v>
       </c>
       <c r="G36">
-        <v>-5.397872136814319</v>
+        <v>-2.623644906541682</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.6927923258128894</v>
       </c>
       <c r="E37">
-        <v>-29.03461658464461</v>
+        <v>-26.42777335128513</v>
       </c>
       <c r="F37">
-        <v>0.06116733014261054</v>
+        <v>0.9366241063216568</v>
       </c>
       <c r="G37">
-        <v>-5.769010776130933</v>
+        <v>-2.577115188987225</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.1626427764159402</v>
       </c>
       <c r="E38">
-        <v>-27.88797526658442</v>
+        <v>-24.95242821890418</v>
       </c>
       <c r="F38">
-        <v>0.525580745745917</v>
+        <v>0.7016626627219938</v>
       </c>
       <c r="G38">
-        <v>-5.62639247429913</v>
+        <v>-2.7538387309646</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.3989945810653016</v>
       </c>
       <c r="E39">
-        <v>-27.39993709430378</v>
+        <v>-24.32482700618114</v>
       </c>
       <c r="F39">
-        <v>0.7933927554383999</v>
+        <v>1.398433963177965</v>
       </c>
       <c r="G39">
-        <v>-5.301432634709809</v>
+        <v>-3.540311792547099</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.9850351834609562</v>
       </c>
       <c r="E40">
-        <v>-26.83381444470888</v>
+        <v>-24.17180986946196</v>
       </c>
       <c r="F40">
-        <v>0.5640476428297176</v>
+        <v>1.371927863023186</v>
       </c>
       <c r="G40">
-        <v>-6.288478408334592</v>
+        <v>-3.519855931659942</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.586811088201793</v>
       </c>
       <c r="E41">
-        <v>-25.29406082651684</v>
+        <v>-23.63242333040834</v>
       </c>
       <c r="F41">
-        <v>0.7987423521256791</v>
+        <v>1.290792589388585</v>
       </c>
       <c r="G41">
-        <v>-5.690987838861389</v>
+        <v>-3.425432551788849</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-2.200572164777136</v>
       </c>
       <c r="E42">
-        <v>-25.65551003638706</v>
+        <v>-24.04171586816961</v>
       </c>
       <c r="F42">
-        <v>0.4753642854208082</v>
+        <v>1.317790739780627</v>
       </c>
       <c r="G42">
-        <v>-5.609833125511695</v>
+        <v>-2.526142719319067</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-2.820058496457604</v>
       </c>
       <c r="E43">
-        <v>-24.66093487550445</v>
+        <v>-22.25268334127733</v>
       </c>
       <c r="F43">
-        <v>0.956471789292733</v>
+        <v>1.449804339295173</v>
       </c>
       <c r="G43">
-        <v>-6.076080427626032</v>
+        <v>-3.530595341389338</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.439390054591018</v>
       </c>
       <c r="E44">
-        <v>-24.50520971132867</v>
+        <v>-22.17904129696459</v>
       </c>
       <c r="F44">
-        <v>1.280232561737697</v>
+        <v>2.002739580663843</v>
       </c>
       <c r="G44">
-        <v>-6.335514639356558</v>
+        <v>-3.72350082996267</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.058561123514551</v>
       </c>
       <c r="E45">
-        <v>-23.720778386772</v>
+        <v>-20.58094281965773</v>
       </c>
       <c r="F45">
-        <v>0.8799919404618659</v>
+        <v>1.443548508669231</v>
       </c>
       <c r="G45">
-        <v>-5.833500203235936</v>
+        <v>-3.5114140405348</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.671748202302897</v>
       </c>
       <c r="E46">
-        <v>-21.72603087113329</v>
+        <v>-21.00560046972701</v>
       </c>
       <c r="F46">
-        <v>1.108912928960315</v>
+        <v>1.960463021894567</v>
       </c>
       <c r="G46">
-        <v>-6.369530494772569</v>
+        <v>-4.331187879696828</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.277013904518808</v>
       </c>
       <c r="E47">
-        <v>-21.51048003684218</v>
+        <v>-19.43412036263723</v>
       </c>
       <c r="F47">
-        <v>1.342134801014099</v>
+        <v>2.042499559263414</v>
       </c>
       <c r="G47">
-        <v>-6.252280903408201</v>
+        <v>-3.620155529863241</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.876183447918001</v>
       </c>
       <c r="E48">
-        <v>-21.14075277648594</v>
+        <v>-18.28254753638269</v>
       </c>
       <c r="F48">
-        <v>1.151868748999886</v>
+        <v>1.84217878371402</v>
       </c>
       <c r="G48">
-        <v>-6.375837084024881</v>
+        <v>-4.049043325566902</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.459048763113536</v>
       </c>
       <c r="E49">
-        <v>-20.71414788259335</v>
+        <v>-17.83868915652088</v>
       </c>
       <c r="F49">
-        <v>0.8522366622636656</v>
+        <v>1.855329944600865</v>
       </c>
       <c r="G49">
-        <v>-6.825283367527415</v>
+        <v>-3.770245732977179</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-7.026234347021869</v>
       </c>
       <c r="E50">
-        <v>-19.62176674009307</v>
+        <v>-17.41440736979423</v>
       </c>
       <c r="F50">
-        <v>1.378939164720481</v>
+        <v>1.7437571391178</v>
       </c>
       <c r="G50">
-        <v>-6.66373536630206</v>
+        <v>-3.736190151014696</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-7.576815255416592</v>
       </c>
       <c r="E51">
-        <v>-19.90061205558938</v>
+        <v>-15.71290118852221</v>
       </c>
       <c r="F51">
-        <v>1.036886383286898</v>
+        <v>2.385703771386888</v>
       </c>
       <c r="G51">
-        <v>-6.561989059698099</v>
+        <v>-4.428256385453798</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.09755026051209</v>
       </c>
       <c r="E52">
-        <v>-17.50850453119961</v>
+        <v>-16.34863554056302</v>
       </c>
       <c r="F52">
-        <v>1.655038990277973</v>
+        <v>1.663279589201022</v>
       </c>
       <c r="G52">
-        <v>-6.571013606838153</v>
+        <v>-4.149730257598296</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.593277609603781</v>
       </c>
       <c r="E53">
-        <v>-18.80460813388296</v>
+        <v>-16.29255491845203</v>
       </c>
       <c r="F53">
-        <v>1.289036450494651</v>
+        <v>2.156989874739139</v>
       </c>
       <c r="G53">
-        <v>-6.786122924343377</v>
+        <v>-5.355818276828956</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.060742281404101</v>
       </c>
       <c r="E54">
-        <v>-17.53567537524563</v>
+        <v>-15.52157769017214</v>
       </c>
       <c r="F54">
-        <v>1.108344668921994</v>
+        <v>1.547177270759449</v>
       </c>
       <c r="G54">
-        <v>-6.776969265927292</v>
+        <v>-4.405459968870377</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.487892905750291</v>
       </c>
       <c r="E55">
-        <v>-17.64411421383331</v>
+        <v>-15.18828653168161</v>
       </c>
       <c r="F55">
-        <v>1.191338799008477</v>
+        <v>1.671395933013652</v>
       </c>
       <c r="G55">
-        <v>-7.901161009607462</v>
+        <v>-4.987318142307141</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.880788817709568</v>
       </c>
       <c r="E56">
-        <v>-16.95394307574629</v>
+        <v>-14.83785509907205</v>
       </c>
       <c r="F56">
-        <v>0.9252373680027749</v>
+        <v>2.091061769885132</v>
       </c>
       <c r="G56">
-        <v>-7.291821997649207</v>
+        <v>-4.687223810263287</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-10.2322957866821</v>
       </c>
       <c r="E57">
-        <v>-16.00914037268198</v>
+        <v>-14.27753342468097</v>
       </c>
       <c r="F57">
-        <v>1.129418335649214</v>
+        <v>2.051600003550569</v>
       </c>
       <c r="G57">
-        <v>-7.61854304746542</v>
+        <v>-4.941861041507409</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-10.53232621119316</v>
       </c>
       <c r="E58">
-        <v>-15.33610045176598</v>
+        <v>-12.97738136623477</v>
       </c>
       <c r="F58">
-        <v>0.8882159720368593</v>
+        <v>1.667668279701054</v>
       </c>
       <c r="G58">
-        <v>-7.354189365063537</v>
+        <v>-5.577661243961058</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-10.78476398086976</v>
       </c>
       <c r="E59">
-        <v>-15.69706964339139</v>
+        <v>-11.64942900585547</v>
       </c>
       <c r="F59">
-        <v>1.072744751419283</v>
+        <v>1.766119745523775</v>
       </c>
       <c r="G59">
-        <v>-7.300525421871952</v>
+        <v>-6.231954153797076</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-10.97608972089337</v>
       </c>
       <c r="E60">
-        <v>-14.69153104693621</v>
+        <v>-12.96230607626323</v>
       </c>
       <c r="F60">
-        <v>1.230103079989882</v>
+        <v>1.831852355670722</v>
       </c>
       <c r="G60">
-        <v>-7.594339649027809</v>
+        <v>-4.99332347191538</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-11.09912823703576</v>
       </c>
       <c r="E61">
-        <v>-14.07116180720342</v>
+        <v>-11.95275978031126</v>
       </c>
       <c r="F61">
-        <v>0.3415158521090612</v>
+        <v>1.190464043031121</v>
       </c>
       <c r="G61">
-        <v>-7.713105470249163</v>
+        <v>-5.628514533989803</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-11.15474597040421</v>
       </c>
       <c r="E62">
-        <v>-13.93469171450827</v>
+        <v>-11.78560927621414</v>
       </c>
       <c r="F62">
-        <v>1.039119661804845</v>
+        <v>1.284119261591633</v>
       </c>
       <c r="G62">
-        <v>-7.736216388658814</v>
+        <v>-6.333352853119414</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-11.12866108104498</v>
       </c>
       <c r="E63">
-        <v>-13.75989261781219</v>
+        <v>-11.66725760802367</v>
       </c>
       <c r="F63">
-        <v>0.6074673486148565</v>
+        <v>1.762483212625485</v>
       </c>
       <c r="G63">
-        <v>-8.083552205548068</v>
+        <v>-5.72459980772161</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-11.02241742339035</v>
       </c>
       <c r="E64">
-        <v>-13.66063752451207</v>
+        <v>-11.45861722506828</v>
       </c>
       <c r="F64">
-        <v>0.4361278350198067</v>
+        <v>1.372045491194383</v>
       </c>
       <c r="G64">
-        <v>-8.01132603351779</v>
+        <v>-6.315886414854218</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-10.83796330155968</v>
       </c>
       <c r="E65">
-        <v>-13.87737029051917</v>
+        <v>-10.67516405089726</v>
       </c>
       <c r="F65">
-        <v>0.4896569365887108</v>
+        <v>1.336226884697333</v>
       </c>
       <c r="G65">
-        <v>-8.33997051029232</v>
+        <v>-6.347657720394604</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-10.56491194480864</v>
       </c>
       <c r="E66">
-        <v>-12.90627073889232</v>
+        <v>-11.13460038134545</v>
       </c>
       <c r="F66">
-        <v>0.3085774790715445</v>
+        <v>0.9742965990661727</v>
       </c>
       <c r="G66">
-        <v>-8.937153199030369</v>
+        <v>-7.291159888541354</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-10.21369062370134</v>
       </c>
       <c r="E67">
-        <v>-12.299754101149</v>
+        <v>-11.73864447228059</v>
       </c>
       <c r="F67">
-        <v>0.2420115313173818</v>
+        <v>1.393437251004278</v>
       </c>
       <c r="G67">
-        <v>-8.083015897170707</v>
+        <v>-6.142493281689351</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.788018999571943</v>
       </c>
       <c r="E68">
-        <v>-13.18462245072179</v>
+        <v>-10.24209249612172</v>
       </c>
       <c r="F68">
-        <v>0.0652685771538709</v>
+        <v>0.9812018697359094</v>
       </c>
       <c r="G68">
-        <v>-8.125142589157933</v>
+        <v>-6.014643323508237</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.285213837234318</v>
       </c>
       <c r="E69">
-        <v>-12.19904083921841</v>
+        <v>-10.98687703074124</v>
       </c>
       <c r="F69">
-        <v>-0.1197978126729695</v>
+        <v>0.9372420684041453</v>
       </c>
       <c r="G69">
-        <v>-7.78307053967612</v>
+        <v>-5.437866837474254</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.723650702147223</v>
       </c>
       <c r="E70">
-        <v>-12.53009040307514</v>
+        <v>-9.478301956092006</v>
       </c>
       <c r="F70">
-        <v>-0.3581215995605956</v>
+        <v>0.5342926857211594</v>
       </c>
       <c r="G70">
-        <v>-7.445510763764333</v>
+        <v>-5.10288266599202</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.110786952287112</v>
       </c>
       <c r="E71">
-        <v>-13.39406437357655</v>
+        <v>-10.52632669568716</v>
       </c>
       <c r="F71">
-        <v>-0.3667299936104881</v>
+        <v>0.02506873546341369</v>
       </c>
       <c r="G71">
-        <v>-8.449668747281608</v>
+        <v>-5.851992910618304</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.451224943611942</v>
       </c>
       <c r="E72">
-        <v>-13.21068834710995</v>
+        <v>-10.28786178291724</v>
       </c>
       <c r="F72">
-        <v>-0.4862940594283603</v>
+        <v>0.4883274069072176</v>
       </c>
       <c r="G72">
-        <v>-7.796438522563697</v>
+        <v>-4.488455345539906</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.763234118772393</v>
       </c>
       <c r="E73">
-        <v>-12.8968696268524</v>
+        <v>-10.79620563264828</v>
       </c>
       <c r="F73">
-        <v>-0.6223815698298742</v>
+        <v>0.4644795377480226</v>
       </c>
       <c r="G73">
-        <v>-7.045732594987484</v>
+        <v>-5.679155949104034</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.049310553341859</v>
       </c>
       <c r="E74">
-        <v>-12.28420784988067</v>
+        <v>-10.65438741215007</v>
       </c>
       <c r="F74">
-        <v>-1.024273955706888</v>
+        <v>0.3395716738146908</v>
       </c>
       <c r="G74">
-        <v>-7.33746448899914</v>
+        <v>-4.450993212217513</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.312872802977591</v>
       </c>
       <c r="E75">
-        <v>-13.65056619831901</v>
+        <v>-11.16723709351873</v>
       </c>
       <c r="F75">
-        <v>-0.2519555481156026</v>
+        <v>0.4423008289054687</v>
       </c>
       <c r="G75">
-        <v>-5.862169527606024</v>
+        <v>-4.509636215900163</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.562113326916925</v>
       </c>
       <c r="E76">
-        <v>-12.7888881641395</v>
+        <v>-10.66894645608473</v>
       </c>
       <c r="F76">
-        <v>-0.3718219680354967</v>
+        <v>0.2949856267264102</v>
       </c>
       <c r="G76">
-        <v>-6.997825690488691</v>
+        <v>-4.860921513617767</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.796767092878068</v>
       </c>
       <c r="E77">
-        <v>-13.37495421326418</v>
+        <v>-11.0633674852048</v>
       </c>
       <c r="F77">
-        <v>-0.5619372571824</v>
+        <v>0.1669564744193298</v>
       </c>
       <c r="G77">
-        <v>-6.262530352397785</v>
+        <v>-4.352673320246698</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.022942262020892</v>
       </c>
       <c r="E78">
-        <v>-14.68799430873622</v>
+        <v>-12.17957745793344</v>
       </c>
       <c r="F78">
-        <v>-0.794853461664551</v>
+        <v>-0.2735096679364457</v>
       </c>
       <c r="G78">
-        <v>-6.635370612121585</v>
+        <v>-3.075411882467246</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.247945396461023</v>
       </c>
       <c r="E79">
-        <v>-15.08827518322221</v>
+        <v>-13.04835161088298</v>
       </c>
       <c r="F79">
-        <v>-1.328415674583949</v>
+        <v>0.02472910482826589</v>
       </c>
       <c r="G79">
-        <v>-5.438038985842296</v>
+        <v>-3.698671738418136</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.47730410454141</v>
       </c>
       <c r="E80">
-        <v>-15.16608342362201</v>
+        <v>-13.81368636054931</v>
       </c>
       <c r="F80">
-        <v>-1.096779297739123</v>
+        <v>0.01789258865296157</v>
       </c>
       <c r="G80">
-        <v>-5.106232938077762</v>
+        <v>-2.58072699417057</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.7206798454057276</v>
       </c>
       <c r="E81">
-        <v>-15.79680928341033</v>
+        <v>-12.80444347235584</v>
       </c>
       <c r="F81">
-        <v>-1.011301722179048</v>
+        <v>0.1800827842840908</v>
       </c>
       <c r="G81">
-        <v>-4.708414612260162</v>
+        <v>-2.670909565205856</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.01590759660533388</v>
       </c>
       <c r="E82">
-        <v>-16.58840465384714</v>
+        <v>-13.78862578539086</v>
       </c>
       <c r="F82">
-        <v>-0.7585908502395998</v>
+        <v>-0.427469205053359</v>
       </c>
       <c r="G82">
-        <v>-3.797521317675234</v>
+        <v>-2.196928828711783</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.7335004278046595</v>
       </c>
       <c r="E83">
-        <v>-17.52132464111533</v>
+        <v>-15.29509511962653</v>
       </c>
       <c r="F83">
-        <v>-0.7971919428426539</v>
+        <v>-0.1458565944302363</v>
       </c>
       <c r="G83">
-        <v>-4.26495048454709</v>
+        <v>-1.96896135233203</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.436565220923212</v>
       </c>
       <c r="E84">
-        <v>-18.12634688243612</v>
+        <v>-15.78639379319269</v>
       </c>
       <c r="F84">
-        <v>-1.11368296296065</v>
+        <v>0.09179787159592787</v>
       </c>
       <c r="G84">
-        <v>-4.601728971711609</v>
+        <v>-1.172708939226524</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.130653100952336</v>
       </c>
       <c r="E85">
-        <v>-18.32733867279256</v>
+        <v>-16.9133271923715</v>
       </c>
       <c r="F85">
-        <v>-1.168144806225106</v>
+        <v>-0.13769386204305</v>
       </c>
       <c r="G85">
-        <v>-3.806112183349643</v>
+        <v>-1.298983077730945</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.81718076982484</v>
       </c>
       <c r="E86">
-        <v>-20.26535346606318</v>
+        <v>-16.65468792789741</v>
       </c>
       <c r="F86">
-        <v>-1.291367770861144</v>
+        <v>-0.07648082444577771</v>
       </c>
       <c r="G86">
-        <v>-4.107808819434505</v>
+        <v>-1.123699623063153</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.4943545278689</v>
       </c>
       <c r="E87">
-        <v>-20.64264780648625</v>
+        <v>-18.67170647870585</v>
       </c>
       <c r="F87">
-        <v>-1.05161256510148</v>
+        <v>-0.3072822069485815</v>
       </c>
       <c r="G87">
-        <v>-3.916376523626148</v>
+        <v>-1.392737727403105</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.156102546748259</v>
       </c>
       <c r="E88">
-        <v>-22.05094435270962</v>
+        <v>-20.0688856212404</v>
       </c>
       <c r="F88">
-        <v>-1.259166644812119</v>
+        <v>-0.1692637721311419</v>
       </c>
       <c r="G88">
-        <v>-4.242879077436769</v>
+        <v>-0.5898708443101347</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.794410323343234</v>
       </c>
       <c r="E89">
-        <v>-22.85843466691336</v>
+        <v>-20.61183606933805</v>
       </c>
       <c r="F89">
-        <v>-1.119875837663979</v>
+        <v>-0.6530651267969708</v>
       </c>
       <c r="G89">
-        <v>-3.707901539381624</v>
+        <v>-1.687690782224471</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.400916057521474</v>
       </c>
       <c r="E90">
-        <v>-24.79806612540472</v>
+        <v>-22.67471900489618</v>
       </c>
       <c r="F90">
-        <v>-1.1001457828641</v>
+        <v>-0.8263736697084749</v>
       </c>
       <c r="G90">
-        <v>-3.260736221755647</v>
+        <v>-0.8395952259739782</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.959849393667657</v>
       </c>
       <c r="E91">
-        <v>-26.49825452074051</v>
+        <v>-24.38611990187496</v>
       </c>
       <c r="F91">
-        <v>-1.123679700777634</v>
+        <v>-0.4029660972785497</v>
       </c>
       <c r="G91">
-        <v>-3.688034955600457</v>
+        <v>-0.5841369794361171</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>6.45789323005765</v>
       </c>
       <c r="E92">
-        <v>-27.79875980015931</v>
+        <v>-26.18172324455237</v>
       </c>
       <c r="F92">
-        <v>-1.395763601166354</v>
+        <v>-0.3753541266410337</v>
       </c>
       <c r="G92">
-        <v>-3.252400268087762</v>
+        <v>-1.323020948891592</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.880277940465362</v>
       </c>
       <c r="E93">
-        <v>-29.61064074265729</v>
+        <v>-27.64340597085217</v>
       </c>
       <c r="F93">
-        <v>-1.461145811901917</v>
+        <v>-0.9979857161790457</v>
       </c>
       <c r="G93">
-        <v>-3.258114269688544</v>
+        <v>-1.137991248156187</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>7.204141503841233</v>
       </c>
       <c r="E94">
-        <v>-31.29455153817251</v>
+        <v>-29.03543623844</v>
       </c>
       <c r="F94">
-        <v>-1.187022470967504</v>
+        <v>-0.6230426070173083</v>
       </c>
       <c r="G94">
-        <v>-3.091600450154282</v>
+        <v>-1.65648889051684</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>7.419916975482068</v>
       </c>
       <c r="E95">
-        <v>-33.72366575215295</v>
+        <v>-30.45415506759204</v>
       </c>
       <c r="F95">
-        <v>-1.286727256670661</v>
+        <v>-0.7352035533563613</v>
       </c>
       <c r="G95">
-        <v>-3.757725249747655</v>
+        <v>-1.055326926040585</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>7.506946796032855</v>
       </c>
       <c r="E96">
-        <v>-34.21753207048147</v>
+        <v>-32.85909628731954</v>
       </c>
       <c r="F96">
-        <v>-1.899755582908018</v>
+        <v>-1.365615997908869</v>
       </c>
       <c r="G96">
-        <v>-3.687104692303922</v>
+        <v>-2.406632025351377</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>7.46130435672216</v>
       </c>
       <c r="E97">
-        <v>-35.89765253325226</v>
+        <v>-35.71454142251511</v>
       </c>
       <c r="F97">
-        <v>-1.504577114830695</v>
+        <v>-1.092379010095452</v>
       </c>
       <c r="G97">
-        <v>-4.337381910400804</v>
+        <v>-2.10486917835573</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>7.260954264480495</v>
       </c>
       <c r="E98">
-        <v>-39.65370246519728</v>
+        <v>-37.95256082608288</v>
       </c>
       <c r="F98">
-        <v>-1.252789044177965</v>
+        <v>-1.358823385205913</v>
       </c>
       <c r="G98">
-        <v>-3.276630150889688</v>
+        <v>-2.487737080517982</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>6.938746625668401</v>
       </c>
       <c r="E99">
-        <v>-40.89749540038103</v>
+        <v>-39.33851841002642</v>
       </c>
       <c r="F99">
-        <v>-1.576717975205698</v>
+        <v>-1.6706366146003</v>
       </c>
       <c r="G99">
-        <v>-4.488941995734178</v>
+        <v>-2.223863427219293</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>6.440495648609248</v>
       </c>
       <c r="E100">
-        <v>-43.83520932287395</v>
+        <v>-41.41621624830064</v>
       </c>
       <c r="F100">
-        <v>-1.480831963229447</v>
+        <v>-1.920731502281708</v>
       </c>
       <c r="G100">
-        <v>-4.497046211214315</v>
+        <v>-2.607744356316562</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>5.870494902245095</v>
       </c>
       <c r="E101">
-        <v>-44.99778634096713</v>
+        <v>-43.00905943152161</v>
       </c>
       <c r="F101">
-        <v>-1.528169018462425</v>
+        <v>-1.956470585508089</v>
       </c>
       <c r="G101">
-        <v>-5.300969158334311</v>
+        <v>-3.10887156623266</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.092756493681984</v>
       </c>
       <c r="E102">
-        <v>-48.09536671711583</v>
+        <v>-46.27132455767025</v>
       </c>
       <c r="F102">
-        <v>-1.616808472398986</v>
+        <v>-2.232265571861351</v>
       </c>
       <c r="G102">
-        <v>-5.715889762407787</v>
+        <v>-2.787755270014433</v>
       </c>
     </row>
   </sheetData>
